--- a/Test_Results_12-25-2025.xlsx
+++ b/Test_Results_12-25-2025.xlsx
@@ -425,101 +425,101 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:T1"/>
+  <dimension ref="A1:S1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Open_stock</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Open_stock</t>
+          <t>High_stock</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>High_stock</t>
+          <t>Low_stock</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Low_stock</t>
+          <t>Close_stock</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Close_stock</t>
+          <t>Price Change_stock</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Price Change_stock</t>
+          <t>Is_Earnings_Date_stock</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Is_Earnings_Date_stock</t>
+          <t>Open_benchmark</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Open_benchmark</t>
+          <t>High_benchmark</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>High_benchmark</t>
+          <t>Low_benchmark</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Low_benchmark</t>
+          <t>Close_benchmark</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Close_benchmark</t>
+          <t>Price Change_benchmark</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Price Change_benchmark</t>
+          <t>Is_Earnings_Date_benchmark</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Is_Earnings_Date_benchmark</t>
+          <t>Next_Day_Close</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Next_Day_Close</t>
+          <t>Next_Day_Stock_Change</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Next_Day_Stock_Change</t>
+          <t>Next_Day_Bench_Change</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Next_Day_Bench_Change</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>1-day Return</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>1-day Return</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>ticker</t>
         </is>
